--- a/Backtest/02-01-19/NASDAQstock_02-01-19period252RS90.xlsx
+++ b/Backtest/02-01-19/NASDAQstock_02-01-19period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Backtest/02-01-19/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70327C1-CD76-6444-A32D-B82F030D35B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -208,12 +214,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -221,8 +227,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -268,17 +281,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -316,7 +337,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -350,6 +371,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -384,9 +406,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -559,9 +582,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
@@ -693,7 +716,7 @@
         <v>3.84</v>
       </c>
       <c r="F2">
-        <v>0.2826188805275011</v>
+        <v>0.28261888052750112</v>
       </c>
       <c r="G2">
         <v>4.83</v>
@@ -705,19 +728,19 @@
         <v>26.67399978637695</v>
       </c>
       <c r="J2">
-        <v>25.85149984359741</v>
+        <v>25.851499843597409</v>
       </c>
       <c r="K2">
         <v>24.51059997558594</v>
       </c>
       <c r="L2">
-        <v>19.70559998035431</v>
+        <v>19.705599980354311</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -756,7 +779,7 @@
         <v>843.75</v>
       </c>
       <c r="AB2">
-        <v>142.86</v>
+        <v>142.86000000000001</v>
       </c>
       <c r="AC2">
         <v>124.24</v>
@@ -768,10 +791,10 @@
         <v>-78.38</v>
       </c>
       <c r="AF2">
-        <v>146.67</v>
+        <v>146.66999999999999</v>
       </c>
       <c r="AG2">
-        <v>145.45</v>
+        <v>145.44999999999999</v>
       </c>
       <c r="AH2" t="s">
         <v>44</v>
@@ -783,7 +806,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>76.25476125083671</v>
+        <v>76.254761250836708</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -791,7 +814,7 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>97.59433962264151</v>
+        <v>97.594339622641513</v>
       </c>
       <c r="C3">
         <v>1251</v>
@@ -809,25 +832,25 @@
         <v>4.95</v>
       </c>
       <c r="H3">
-        <v>1.286283464024712</v>
+        <v>1.2862834640247121</v>
       </c>
       <c r="I3">
         <v>26.07600021362305</v>
       </c>
       <c r="J3">
-        <v>26.51350002288818</v>
+        <v>26.513500022888181</v>
       </c>
       <c r="K3">
         <v>23.91919994354248</v>
       </c>
       <c r="L3">
-        <v>20.08320002555847</v>
+        <v>20.083200025558469</v>
       </c>
       <c r="M3">
         <v>0.98</v>
       </c>
       <c r="N3">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -893,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>66.66666666666666</v>
+        <v>66.666666666666657</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -901,7 +924,7 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>92.68867924528303</v>
+        <v>92.688679245283026</v>
       </c>
       <c r="C4">
         <v>54</v>
@@ -913,25 +936,25 @@
         <v>1.67</v>
       </c>
       <c r="F4">
-        <v>-0.8776461992597264</v>
+        <v>-0.87764619925972642</v>
       </c>
       <c r="G4">
         <v>1.45</v>
       </c>
       <c r="H4">
-        <v>-1.23281684521633</v>
+        <v>-1.2328168452163299</v>
       </c>
       <c r="I4">
-        <v>71.8988540649414</v>
+        <v>71.898854064941403</v>
       </c>
       <c r="J4">
-        <v>72.4317741394043</v>
+        <v>72.431774139404297</v>
       </c>
       <c r="K4">
-        <v>71.41984710693359</v>
+        <v>71.419847106933588</v>
       </c>
       <c r="L4">
-        <v>63.0511449432373</v>
+        <v>63.051144943237297</v>
       </c>
       <c r="M4">
         <v>0.99</v>
@@ -1003,7 +1026,7 @@
         <v>58</v>
       </c>
       <c r="AK4">
-        <v>57.45825726975693</v>
+        <v>57.458257269756928</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1011,7 +1034,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>95.35377358490567</v>
+        <v>95.353773584905667</v>
       </c>
       <c r="C5">
         <v>2334</v>
@@ -1023,25 +1046,25 @@
         <v>2.29</v>
       </c>
       <c r="F5">
-        <v>-0.5461418907490899</v>
+        <v>-0.54614189074908992</v>
       </c>
       <c r="G5">
         <v>2.04</v>
       </c>
       <c r="H5">
-        <v>-0.8081685073728403</v>
+        <v>-0.80816850737284029</v>
       </c>
       <c r="I5">
-        <v>65.21800003051757</v>
+        <v>65.218000030517572</v>
       </c>
       <c r="J5">
-        <v>62.02149982452393</v>
+        <v>62.021499824523929</v>
       </c>
       <c r="K5">
-        <v>60.33220008850098</v>
+        <v>60.332200088500983</v>
       </c>
       <c r="L5">
-        <v>57.00985000610351</v>
+        <v>57.009850006103512</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1092,10 +1115,10 @@
         <v>361.54</v>
       </c>
       <c r="AD5">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="AE5">
-        <v>71.43000000000001</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="AF5">
         <v>-31.37</v>
@@ -1113,7 +1136,7 @@
         <v>59</v>
       </c>
       <c r="AK5">
-        <v>46.30213326424466</v>
+        <v>46.302133264244659</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1133,19 +1156,19 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>-0.7012003576330973</v>
+        <v>-0.70120035763309729</v>
       </c>
       <c r="G6">
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>0.0987076039539346</v>
+        <v>9.8707603953934603E-2</v>
       </c>
       <c r="I6">
         <v>28.4379997253418</v>
       </c>
       <c r="J6">
-        <v>27.47699985504151</v>
+        <v>27.476999855041509</v>
       </c>
       <c r="K6">
         <v>26.98840003967285</v>
@@ -1223,7 +1246,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>35.87941692430381</v>
+        <v>35.879416924303811</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1240,25 +1263,25 @@
         <v>13.87</v>
       </c>
       <c r="E7">
-        <v>4.14</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F7">
-        <v>0.4430241910971637</v>
+        <v>0.44302419109716368</v>
       </c>
       <c r="G7">
         <v>3.53</v>
       </c>
       <c r="H7">
-        <v>0.2642484814183459</v>
+        <v>0.26424848141834589</v>
       </c>
       <c r="I7">
-        <v>13.8920000076294</v>
+        <v>13.892000007629401</v>
       </c>
       <c r="J7">
-        <v>13.82300000190735</v>
+        <v>13.823000001907349</v>
       </c>
       <c r="K7">
-        <v>13.76939998626709</v>
+        <v>13.769399986267089</v>
       </c>
       <c r="L7">
         <v>12.53189998626709</v>
@@ -1303,7 +1326,7 @@
         <v>1.57</v>
       </c>
       <c r="AA7">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="AB7">
         <v>44.44</v>
@@ -1333,7 +1356,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>32.22798661305953</v>
+        <v>32.227986613059528</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1341,7 +1364,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>95.44811320754717</v>
+        <v>95.448113207547166</v>
       </c>
       <c r="C8">
         <v>2641</v>
@@ -1350,28 +1373,28 @@
         <v>178.13</v>
       </c>
       <c r="E8">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F8">
-        <v>-0.5621824218060564</v>
+        <v>-0.56218242180605638</v>
       </c>
       <c r="G8">
         <v>2.04</v>
       </c>
       <c r="H8">
-        <v>-0.8081685073728403</v>
+        <v>-0.80816850737284029</v>
       </c>
       <c r="I8">
-        <v>181.6920013427734</v>
+        <v>181.69200134277341</v>
       </c>
       <c r="J8">
-        <v>177.8170013427734</v>
+        <v>177.81700134277341</v>
       </c>
       <c r="K8">
-        <v>172.3198004150391</v>
+        <v>172.31980041503911</v>
       </c>
       <c r="L8">
-        <v>156.8919998931885</v>
+        <v>156.89199989318851</v>
       </c>
       <c r="M8">
         <v>1.02</v>
@@ -1413,7 +1436,7 @@
         <v>2.48</v>
       </c>
       <c r="AA8">
-        <v>8.539999999999999</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="AB8">
         <v>0.43</v>
@@ -1431,7 +1454,7 @@
         <v>9.52</v>
       </c>
       <c r="AG8">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AH8" t="s">
         <v>49</v>
@@ -1447,6 +1470,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>